--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.23884685064566</v>
+        <v>9.463812613229919</v>
       </c>
       <c r="D2" t="n">
-        <v>58.75090806281045</v>
+        <v>9.547022560206697</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F2" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.94401734639066</v>
+        <v>3.403402818788482</v>
       </c>
       <c r="D3" t="n">
-        <v>21.41414325220312</v>
+        <v>3.479798278483007</v>
       </c>
       <c r="E3" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F3" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.27629333668151</v>
+        <v>7.519897667210746</v>
       </c>
       <c r="D4" t="n">
-        <v>46.17574435750922</v>
+        <v>7.503558458095248</v>
       </c>
       <c r="E4" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F4" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.90842960159176</v>
+        <v>3.56011981025866</v>
       </c>
       <c r="D5" t="n">
-        <v>22.41942016796129</v>
+        <v>3.64315577729371</v>
       </c>
       <c r="E5" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F5" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.07424927457279</v>
+        <v>6.999565507118078</v>
       </c>
       <c r="D6" t="n">
-        <v>43.55925388453421</v>
+        <v>7.07837875623681</v>
       </c>
       <c r="E6" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F6" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.3305967419403</v>
+        <v>8.016221970565299</v>
       </c>
       <c r="D7" t="n">
-        <v>49.72697917545946</v>
+        <v>8.080634116012163</v>
       </c>
       <c r="E7" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F7" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.44906434126546</v>
+        <v>4.785472955455638</v>
       </c>
       <c r="D8" t="n">
-        <v>29.82127890534109</v>
+        <v>4.845957822117927</v>
       </c>
       <c r="E8" t="n">
-        <v>13.38292881814436</v>
+        <v>2.174725932948459</v>
       </c>
       <c r="F8" t="n">
-        <v>13.33999524545368</v>
+        <v>2.167749227386224</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
